--- a/docs/analytics/customer-product-tracker-2026-08-06.xlsx
+++ b/docs/analytics/customer-product-tracker-2026-08-06.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-06T06:40</t>
+          <t>2026-08-06T07:01</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>בבקה דיזינגוף 145 (בבקה בייקרי בע"מ)</t>
+          <t>בבקה דיזינגוף 274 (בבקה בייקרי בע"מ)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -72794,7 +72794,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>אחר</t>
+          <t>DESERTEA</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
@@ -72928,7 +72928,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ELITA</t>
+          <t>COCKTAIL</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -73651,7 +73651,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>אחר</t>
+          <t>שירותים והתחשבנות</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
@@ -74452,7 +74452,7 @@
         <v>84</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>13068</v>
+        <v>13165</v>
       </c>
       <c r="E2" s="9" t="n">
         <v>72340</v>
@@ -74731,7 +74731,7 @@
         <v>85</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>8014</v>
+        <v>9702</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>44712</v>
@@ -74781,22 +74781,22 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>נונומימי כיכר המושבה בע"מ (הוד השרון)</t>
+          <t>א.ע. עידן אחזקות והשקעות בע"מ (מלון בוטניקה)</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>CALM</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>5655</v>
+        <v>7155</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>82784.12</v>
+        <v>44712</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -74805,29 +74805,29 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>0533037488</t>
+          <t>04-8508838</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>מימי ואזה חנויות</t>
+          <t>בני ציון הבימה בע"מ (קבוצת נורדוי)</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>NAMASTEA</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>5428</v>
+        <v>7155</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>32205.8</v>
+        <v>42444.6</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
@@ -74836,29 +74836,29 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>054-500-0144</t>
+          <t>0507766473</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>קפה אניצ'ה בע"מ</t>
+          <t>מימי ואזה חנויות</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>NAMASTEA</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>5428</v>
+        <v>6878</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>32175</v>
+        <v>32205.8</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -74867,29 +74867,29 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>0504302003</t>
+          <t>054-500-0144</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>מימי ואזה חנויות</t>
+          <t>נונומימי כיכר המושבה בע"מ (הוד השרון)</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>MATCHA</t>
+          <t>CALM</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>5420</v>
+        <v>5655</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>32205.8</v>
+        <v>82784.12</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -74898,29 +74898,29 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>054-500-0144</t>
+          <t>0533037488</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>בר קפה 58 (רח' רש"י)</t>
+          <t>מימי ואזה חנויות</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>MATCHA</t>
+          <t>NAMASTEA</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>5130</v>
+        <v>5428</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>67737.41</v>
+        <v>32205.8</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
@@ -74929,60 +74929,60 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>0545865518</t>
+          <t>054-500-0144</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>וויקס.קום בע"מ (קמפוס וויקס)</t>
+          <t>קפה אניצ'ה בע"מ</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>MATCHA</t>
+          <t>NAMASTEA</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>5130</v>
+        <v>5428</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>64146</v>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>בסכנה</t>
+        <v>32175</v>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>פעיל</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>052-668-6444</t>
+          <t>0504302003</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>פודטראק בייקרי במתחם האלף (אר.טו.אם קורפוראשיין בע"מ)</t>
+          <t>בר קפה 58 (רח' רש"י)</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>MUZA</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>4890</v>
+        <v>5395</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>127074</v>
+        <v>67737.41</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -74991,14 +74991,14 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>050-977-7387</t>
+          <t>0545865518</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>א.ע. עידן אחזקות והשקעות בע"מ (מלון בוטניקה)</t>
+          <t>וויקס.קום בע"מ (קמפוס וויקס)</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -75007,29 +75007,29 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>4890</v>
+        <v>5395</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>44712</v>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+        <v>64146</v>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>בסכנה</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>04-8508838</t>
+          <t>052-668-6444</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>בני ציון הבימה בע"מ (קבוצת נורדוי)</t>
+          <t>בני הכיכר 48 בע"מ (OPEN)</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -75038,44 +75038,40 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>4890</v>
+        <v>5390</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>42444.6</v>
+        <v>26851.4</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
           <t>פעיל</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>0507766473</t>
-        </is>
-      </c>
+      <c r="G21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>קפה אנסטסיה בע״מ</t>
+          <t>נורדוי הבימה בע״מ (נורדיניו)</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>DETOX</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>4876</v>
+        <v>5390</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>25720</v>
+        <v>26082</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
@@ -75084,14 +75080,14 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>0508508720</t>
+          <t>0547603050</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>וויקס.קום בע"מ (קמפוס וויקס)</t>
+          <t>פודטראק בייקרי במתחם האלף (אר.טו.אם קורפוראשיין בע"מ)</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -75100,60 +75096,60 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>4677</v>
+        <v>5060</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>64146</v>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>בסכנה</t>
+        <v>127074</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>פעיל</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>052-668-6444</t>
+          <t>050-977-7387</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>מוזה קוקטיילים בע"מ</t>
+          <t>קפה אנסטסיה בע״מ</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>MUZA</t>
+          <t>DETOX</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>4502</v>
+        <v>4876</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>72340</v>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>בסכנה</t>
+        <v>25720</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>פעיל</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>0529928877</t>
+          <t>0508508720</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>דניאל שור (קפה פיורי)</t>
+          <t>וויקס.קום בע"מ (קמפוס וויקס)</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -75162,44 +75158,44 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>4502</v>
+        <v>4449</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>50291.58</v>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+        <v>64146</v>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>בסכנה</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>0522586899</t>
+          <t>052-668-6444</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>קפה אניצ'ה בע"מ</t>
+          <t>דניאל שור (קפה פיורי)</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>FRESH</t>
+          <t>MUZA</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4088</v>
+        <v>4420</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>32175</v>
+        <v>50291.58</v>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
@@ -75208,29 +75204,29 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>0504302003</t>
+          <t>0522586899</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>נונומימי הרצליה בע"מ</t>
+          <t>שי קדוש (קבוצת מור דן פוד בע"מ)</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>CALM</t>
+          <t>MUZA</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>3996</v>
+        <v>4158</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>63220.23</v>
+        <v>87697.09</v>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
@@ -75239,72 +75235,76 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>052-459-1925</t>
+          <t>0502003050</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>מוזה קוקטיילים בע"מ</t>
+          <t>קפה אניצ'ה בע"מ</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>MATCHA</t>
+          <t>FRESH</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>3900</v>
+        <v>4088</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>72340</v>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>בסכנה</t>
+        <v>32175</v>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>פעיל</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>0529928877</t>
+          <t>0504302003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>בני הכיכר 48 בע"מ (OPEN)</t>
+          <t>נונומימי הרצליה בע"מ</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>MATCHA</t>
+          <t>CALM</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>3900</v>
+        <v>3996</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>26851.4</v>
+        <v>63220.23</v>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
           <t>פעיל</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>052-459-1925</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>נורדוי הבימה בע״מ (נורדיניו)</t>
+          <t>מוזה קוקטיילים בע"מ</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -75313,44 +75313,44 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>3900</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>26082</v>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+        <v>72340</v>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>בסכנה</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>0547603050</t>
+          <t>0529928877</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>ברדא פוראבר בע"מ</t>
+          <t>עידו א. א. אחזקות והשקעות בע"מ (דנדי רשפון)</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>DETOX</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>3670</v>
+        <v>3685</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>20564.75</v>
+        <v>22470.75</v>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
@@ -75359,29 +75359,29 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>0542100606</t>
+          <t>0505556887</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>עידו א. א. אחזקות והשקעות בע"מ (דנדי רשפון)</t>
+          <t>ברדא פוראבר בע"מ</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>MATCHA</t>
+          <t>DETOX</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3540</v>
+        <v>3670</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>22470.75</v>
+        <v>20564.75</v>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
@@ -75390,7 +75390,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>0505556887</t>
+          <t>0542100606</t>
         </is>
       </c>
     </row>
@@ -75406,10 +75406,10 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>3340</v>
+        <v>3430</v>
       </c>
       <c r="E33" s="9" t="n">
         <v>20079.75</v>
@@ -75437,10 +75437,10 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>3250</v>
+        <v>3430</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>19448.4</v>
@@ -75459,53 +75459,53 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>קפה אנסטסיה בע״מ</t>
+          <t>ר.י.א שירותי מזון בע"מ (ג׳אפן ג׳אפן אופקים)</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>NAMASTEA</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>3149</v>
+        <v>3180</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>25720</v>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>פעיל</t>
+        <v>16570.4</v>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>בסכנה</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>0508508720</t>
+          <t>0523628057</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>סטקיית הבוקרים הנועזים בע"מ (סטקיית הבוקרים חיפה)</t>
+          <t>בית העם קונדיטוריה ויין בע"מ</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>DETOX</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>3066</v>
+        <v>3180</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>15201</v>
+        <v>16481</v>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
@@ -75514,29 +75514,29 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>0523601634</t>
+          <t>052-552-6064</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>עידו א. א. אחזקות והשקעות בע"מ (דנדי רשפון)</t>
+          <t>רשת פט אנד פאף בע"מ (הרצליה)</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>NAMASTEA</t>
+          <t>MATCHA</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>3064</v>
+        <v>3180</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>22470.75</v>
+        <v>15372</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
@@ -75545,14 +75545,14 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>0505556887</t>
+          <t>0545969640</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>ר.י.א שירותי מזון בע"מ (ג׳אפן ג׳אפן אופקים)</t>
+          <t>סטקיית הבוקרים הנועזים בע"מ (סטקיית הבוקרים חיפה)</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -75564,26 +75564,26 @@
         <v>60</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>3050</v>
+        <v>3180</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>16570.4</v>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>בסכנה</t>
+        <v>15201</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>פעיל</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>0523628057</t>
+          <t>0523601634</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>בית העם קונדיטוריה ויין בע"מ</t>
+          <t>תרשיש חן בע"מ (ויוינו ראשון לציון)</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -75595,10 +75595,10 @@
         <v>60</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>3050</v>
+        <v>3180</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>16481</v>
+        <v>14558</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
@@ -75607,14 +75607,14 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>052-552-6064</t>
+          <t>050-2105038</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>רשת פט אנד פאף בע"מ (הרצליה)</t>
+          <t>גאפן גאפן באר שבע (א.מ.נ השקעות בש בע"מ)</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -75623,13 +75623,13 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>3050</v>
+        <v>3180</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>15372</v>
+        <v>12973.3</v>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
@@ -75638,29 +75638,29 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>0545969640</t>
+          <t>0506779214</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>סטקיית הבוקרים הנועזים בע"מ (סטקיית הבוקרים חיפה)</t>
+          <t>קפה אנסטסיה בע״מ</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>MATCHA</t>
+          <t>NAMASTEA</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>3050</v>
+        <v>3149</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>15201</v>
+        <v>25720</v>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
@@ -75669,7 +75669,7 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>0523601634</t>
+          <t>0508508720</t>
         </is>
       </c>
     </row>
